--- a/Data/Excel/world_building_income.xlsx
+++ b/Data/Excel/world_building_income.xlsx
@@ -215,16 +215,16 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>200701</v>
+        <v>30020001</v>
       </c>
       <c r="C5">
-        <v>2007</v>
+        <v>30000007</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2003</v>
+        <v>30902003</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -235,16 +235,16 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>201101</v>
+        <v>30020002</v>
       </c>
       <c r="C6">
-        <v>2011</v>
+        <v>30001001</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2108</v>
+        <v>30902013</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -255,16 +255,16 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>201201</v>
+        <v>30020003</v>
       </c>
       <c r="C7">
-        <v>2012</v>
+        <v>30001002</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2110</v>
+        <v>30902014</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -275,16 +275,16 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>201301</v>
+        <v>30020004</v>
       </c>
       <c r="C8">
-        <v>2013</v>
+        <v>30001003</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2107</v>
+        <v>30902012</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -295,16 +295,16 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>202101</v>
+        <v>30020005</v>
       </c>
       <c r="C9">
-        <v>2021</v>
+        <v>30002001</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>2102</v>
+        <v>30902009</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -315,16 +315,16 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>202201</v>
+        <v>30020006</v>
       </c>
       <c r="C10">
-        <v>2022</v>
+        <v>30002002</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>2105</v>
+        <v>30902010</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -335,16 +335,16 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>202301</v>
+        <v>30020007</v>
       </c>
       <c r="C11">
-        <v>2023</v>
+        <v>30002003</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>2106</v>
+        <v>30902011</v>
       </c>
       <c r="F11">
         <v>1</v>
